--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.39861728378861</v>
+        <v>4.77727530861565</v>
       </c>
       <c r="D2" t="n">
-        <v>29.76319433531887</v>
+        <v>4.836519079489316</v>
       </c>
       <c r="E2" t="n">
-        <v>4.516189324511531</v>
+        <v>0.733880765233124</v>
       </c>
       <c r="F2" t="n">
-        <v>4.360764968799017</v>
+        <v>0.7086243074298402</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.80837411537911</v>
+        <v>4.843860793749106</v>
       </c>
       <c r="D3" t="n">
-        <v>30.06682314874777</v>
+        <v>4.885858761671512</v>
       </c>
       <c r="E3" t="n">
-        <v>4.516189324511531</v>
+        <v>0.733880765233124</v>
       </c>
       <c r="F3" t="n">
-        <v>4.360764968799017</v>
+        <v>0.7086243074298402</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.48609797671079</v>
+        <v>3.653990921215504</v>
       </c>
       <c r="D4" t="n">
-        <v>22.67973246126339</v>
+        <v>3.685456524955301</v>
       </c>
       <c r="E4" t="n">
-        <v>4.516189324511531</v>
+        <v>0.733880765233124</v>
       </c>
       <c r="F4" t="n">
-        <v>4.360764968799017</v>
+        <v>0.7086243074298402</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.14802975129789</v>
+        <v>4.899054834585908</v>
       </c>
       <c r="D5" t="n">
-        <v>29.31835245800711</v>
+        <v>4.764232274426154</v>
       </c>
       <c r="E5" t="n">
-        <v>4.516189324511531</v>
+        <v>0.733880765233124</v>
       </c>
       <c r="F5" t="n">
-        <v>4.360764968799017</v>
+        <v>0.7086243074298402</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.3837509331898</v>
+        <v>3.474859526643342</v>
       </c>
       <c r="D6" t="n">
-        <v>21.22025409363445</v>
+        <v>3.448291290215598</v>
       </c>
       <c r="E6" t="n">
-        <v>4.516189324511531</v>
+        <v>0.733880765233124</v>
       </c>
       <c r="F6" t="n">
-        <v>4.360764968799017</v>
+        <v>0.7086243074298402</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.2200039040104</v>
+        <v>3.44825063440169</v>
       </c>
       <c r="D7" t="n">
-        <v>21.41442468048855</v>
+        <v>3.479844010579389</v>
       </c>
       <c r="E7" t="n">
-        <v>4.516189324511531</v>
+        <v>0.733880765233124</v>
       </c>
       <c r="F7" t="n">
-        <v>4.360764968799017</v>
+        <v>0.7086243074298402</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.62438535991785</v>
+        <v>3.02646262098665</v>
       </c>
       <c r="D8" t="n">
-        <v>19.18272973549727</v>
+        <v>3.117193582018306</v>
       </c>
       <c r="E8" t="n">
-        <v>4.516189324511531</v>
+        <v>0.733880765233124</v>
       </c>
       <c r="F8" t="n">
-        <v>4.360764968799017</v>
+        <v>0.7086243074298402</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
